--- a/Timing_Data.xlsx
+++ b/Timing_Data.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cofc-my.sharepoint.com/personal/balljc1_g_cofc_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jayball/Desktop/Zenodo-Edit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{80505A25-FE28-3641-9B0F-55F05CFDF224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272D7925-197D-6348-AC50-A126CC1334ED}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F935A5F-4500-6E4F-BAF0-67AEA164E1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="900" windowWidth="29260" windowHeight="16340" xr2:uid="{3DCDF51B-F4E9-A841-92FF-3980C9C84320}"/>
+    <workbookView xWindow="0" yWindow="820" windowWidth="29260" windowHeight="16340" xr2:uid="{3DCDF51B-F4E9-A841-92FF-3980C9C84320}"/>
   </bookViews>
   <sheets>
     <sheet name="Glucose3" sheetId="2" r:id="rId1"/>
     <sheet name="Gluecard3" sheetId="3" r:id="rId2"/>
     <sheet name="Lingeling" sheetId="4" r:id="rId3"/>
-    <sheet name="Coarse_Fine" sheetId="1" r:id="rId4"/>
+    <sheet name="Glucose3_Coarse_Fine" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -110,10 +110,10 @@
     <t>Lingeling Timing Data</t>
   </si>
   <si>
-    <t>Coarse/Fine Model Timing Data</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Glucose3 Solver: Coarse/Fine Model Timing Data</t>
   </si>
 </sst>
 </file>
@@ -241,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -260,37 +260,37 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -308,1200 +308,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="78">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFA3A3A3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFA3A3A3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFA3A3A3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFA3A3A3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFA3A3A3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFA3A3A3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFA3A3A3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top/>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFA3A3A3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFA3A3A3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFA3A3A3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1653,13 +464,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FFA3A3A3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color rgb="FFA3A3A3"/>
         </left>
@@ -1669,6 +473,13 @@
         <top style="medium">
           <color rgb="FFA3A3A3"/>
         </top>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FFA3A3A3"/>
         </bottom>
@@ -1698,30 +509,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1837,9 +624,394 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="medium">
+          <color rgb="FFA3A3A3"/>
+        </left>
+        <top style="medium">
+          <color rgb="FFA3A3A3"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="medium">
           <color rgb="FFA3A3A3"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFA3A3A3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1847,10 +1019,835 @@
         <left style="medium">
           <color rgb="FFA3A3A3"/>
         </left>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
         <top style="medium">
           <color rgb="FFA3A3A3"/>
         </top>
-      </border>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFA3A3A3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFA3A3A3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFA3A3A3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFA3A3A3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.00000000000000000000"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top/>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFA3A3A3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFA3A3A3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFA3A3A3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FFA3A3A3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1865,51 +1862,47 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B864935-8296-8F4A-ABD9-92C36C8F5C85}" name="Table7" displayName="Table7" ref="A4:H11" totalsRowShown="0" headerRowDxfId="9" dataDxfId="10" headerRowBorderDxfId="19" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6B864935-8296-8F4A-ABD9-92C36C8F5C85}" name="Table7" displayName="Table7" ref="A4:H11" totalsRowShown="0" headerRowDxfId="77" dataDxfId="75" headerRowBorderDxfId="76" tableBorderDxfId="74">
   <autoFilter ref="A4:H11" xr:uid="{6B864935-8296-8F4A-ABD9-92C36C8F5C85}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{2F7701D9-3F5F-A140-8DBB-D5BE13926458}" name=" " dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{235CFE4B-A5A9-D44E-9939-72134000CA1E}" name="k=1" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{A7302296-AB6E-5547-978B-04BBFAE0643C}" name="k=3" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{0DB31123-2A1D-4B45-8826-8C4753714C10}" name="k=5" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{BDD4631D-3845-C840-A7EB-8D726B060B6C}" name="k=7" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{7F290822-F947-F94E-A58B-A950537A2214}" name="k=10" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{70C72569-58D5-FA45-A340-2B1F46CC5D54}" name="k=13" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{C1BE9CAE-634D-7E4A-81F5-30481EB4050C}" name="k=15" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{2F7701D9-3F5F-A140-8DBB-D5BE13926458}" name=" " dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{235CFE4B-A5A9-D44E-9939-72134000CA1E}" name="k=1" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{A7302296-AB6E-5547-978B-04BBFAE0643C}" name="k=3" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{0DB31123-2A1D-4B45-8826-8C4753714C10}" name="k=5" dataDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{BDD4631D-3845-C840-A7EB-8D726B060B6C}" name="k=7" dataDxfId="69"/>
+    <tableColumn id="6" xr3:uid="{7F290822-F947-F94E-A58B-A950537A2214}" name="k=10" dataDxfId="68"/>
+    <tableColumn id="7" xr3:uid="{70C72569-58D5-FA45-A340-2B1F46CC5D54}" name="k=13" dataDxfId="67"/>
+    <tableColumn id="8" xr3:uid="{C1BE9CAE-634D-7E4A-81F5-30481EB4050C}" name="k=15" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F21216C7-3F21-CA49-9651-CEE8D55F8748}" name="Table8" displayName="Table8" ref="A14:H21" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F21216C7-3F21-CA49-9651-CEE8D55F8748}" name="Table8" displayName="Table8" ref="A14:H21" totalsRowShown="0" headerRowDxfId="65">
   <autoFilter ref="A14:H21" xr:uid="{F21216C7-3F21-CA49-9651-CEE8D55F8748}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{588D7111-AFE1-F546-998E-853D8E327A64}" name=" " dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{ACA159ED-496A-8443-87A3-CC31FB7C2ABC}" name="k=1" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{588D7111-AFE1-F546-998E-853D8E327A64}" name=" " dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{ACA159ED-496A-8443-87A3-CC31FB7C2ABC}" name="k=1" dataDxfId="63">
       <calculatedColumnFormula>B5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B4F953E0-BE02-344D-A1EE-9FC7DA1C96F2}" name="k=3" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{B4F953E0-BE02-344D-A1EE-9FC7DA1C96F2}" name="k=3" dataDxfId="62">
       <calculatedColumnFormula>C5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4C6AC0EA-E9DB-0C44-9EB8-DAA84E39C74C}" name="k=5" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{4C6AC0EA-E9DB-0C44-9EB8-DAA84E39C74C}" name="k=5" dataDxfId="61">
       <calculatedColumnFormula>D5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{3C1B74AD-F0B4-F748-ADDE-C68A74FF1D35}" name="k=7" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{3C1B74AD-F0B4-F748-ADDE-C68A74FF1D35}" name="k=7" dataDxfId="60">
       <calculatedColumnFormula>E5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{646124E3-30C9-E44F-9B6E-9CFE31A51051}" name="k=10" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{646124E3-30C9-E44F-9B6E-9CFE31A51051}" name="k=10" dataDxfId="59">
       <calculatedColumnFormula>F5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{827D59F2-1A4D-E940-AA0A-4A73A11D6387}" name="k=13" dataDxfId="2">
+    <tableColumn id="7" xr3:uid="{827D59F2-1A4D-E940-AA0A-4A73A11D6387}" name="k=13" dataDxfId="58">
       <calculatedColumnFormula>G5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{5156389A-AA0B-0642-9B37-1B8B4F8F9E2B}" name="k=15" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{5156389A-AA0B-0642-9B37-1B8B4F8F9E2B}" name="k=15" dataDxfId="57">
       <calculatedColumnFormula>H5*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1918,46 +1911,46 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D5EB2A49-628A-C041-BB28-85FAE6073ABB}" name="Table5" displayName="Table5" ref="A4:H11" totalsRowShown="0" headerRowDxfId="30" dataDxfId="31" headerRowBorderDxfId="40" tableBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D5EB2A49-628A-C041-BB28-85FAE6073ABB}" name="Table5" displayName="Table5" ref="A4:H11" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53">
   <autoFilter ref="A4:H11" xr:uid="{D5EB2A49-628A-C041-BB28-85FAE6073ABB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{B938DCEE-5027-CF42-8355-488C383E058C}" name=" " dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{949056EC-F28B-E242-B809-DDF099D5CA5A}" name="k=1" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{E02009D6-10FA-8142-84E3-3A714021C1C4}" name="k=3" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{45C7CA65-7DB9-CF41-B593-7317D5DEA269}" name="k=5" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{106DD683-2E4B-D847-BE5E-3AA4C1174515}" name="k=7" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{96A017A1-83F6-9741-8F1F-2971E4DC4F0B}" name="k=10" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{43AC81D4-0602-4348-9F2E-935C4C0B41E6}" name="k=13" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{85B75860-3C4A-D342-816A-BE2F5595628B}" name="k=15" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{B938DCEE-5027-CF42-8355-488C383E058C}" name=" " dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{949056EC-F28B-E242-B809-DDF099D5CA5A}" name="k=1" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{E02009D6-10FA-8142-84E3-3A714021C1C4}" name="k=3" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{45C7CA65-7DB9-CF41-B593-7317D5DEA269}" name="k=5" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{106DD683-2E4B-D847-BE5E-3AA4C1174515}" name="k=7" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{96A017A1-83F6-9741-8F1F-2971E4DC4F0B}" name="k=10" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{43AC81D4-0602-4348-9F2E-935C4C0B41E6}" name="k=13" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{85B75860-3C4A-D342-816A-BE2F5595628B}" name="k=15" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AABBE3C-3742-4E40-A6C7-C4F5BC3FACF5}" name="Table6" displayName="Table6" ref="A14:H21" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2AABBE3C-3742-4E40-A6C7-C4F5BC3FACF5}" name="Table6" displayName="Table6" ref="A14:H21" totalsRowShown="0" headerRowDxfId="44">
   <autoFilter ref="A14:H21" xr:uid="{2AABBE3C-3742-4E40-A6C7-C4F5BC3FACF5}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{F0B9A80C-D0D2-934B-A4CE-972E4328593B}" name=" " dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{A2BF7761-971B-F44F-8C9E-211DBC3F8E6F}" name="k=1" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{F0B9A80C-D0D2-934B-A4CE-972E4328593B}" name=" " dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{A2BF7761-971B-F44F-8C9E-211DBC3F8E6F}" name="k=1" dataDxfId="42">
       <calculatedColumnFormula>B5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9472E5DF-68C0-E747-BDE7-BE9555C6F7CD}" name="k=3" dataDxfId="27">
+    <tableColumn id="3" xr3:uid="{9472E5DF-68C0-E747-BDE7-BE9555C6F7CD}" name="k=3" dataDxfId="41">
       <calculatedColumnFormula>C5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C9E41CDE-F6B8-CA49-BB5E-AEDD0582ADFF}" name="k=5" dataDxfId="26">
+    <tableColumn id="4" xr3:uid="{C9E41CDE-F6B8-CA49-BB5E-AEDD0582ADFF}" name="k=5" dataDxfId="40">
       <calculatedColumnFormula>D5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A27FF3D2-807F-BF46-885B-9134E6FCA1B9}" name="k=7" dataDxfId="25">
+    <tableColumn id="5" xr3:uid="{A27FF3D2-807F-BF46-885B-9134E6FCA1B9}" name="k=7" dataDxfId="39">
       <calculatedColumnFormula>E5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{DD631319-D9FB-6A44-A825-A01E77338FF8}" name="k=10" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{DD631319-D9FB-6A44-A825-A01E77338FF8}" name="k=10" dataDxfId="38">
       <calculatedColumnFormula>F5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8A995B6D-AA23-224E-90DC-105DEE835C6A}" name="k=13" dataDxfId="23">
+    <tableColumn id="7" xr3:uid="{8A995B6D-AA23-224E-90DC-105DEE835C6A}" name="k=13" dataDxfId="37">
       <calculatedColumnFormula>G5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DFDFF614-94AE-F449-BF5A-CD0CF85879F8}" name="k=15" dataDxfId="22">
+    <tableColumn id="8" xr3:uid="{DFDFF614-94AE-F449-BF5A-CD0CF85879F8}" name="k=15" dataDxfId="36">
       <calculatedColumnFormula>H5*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1966,46 +1959,46 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E13F33F7-DB49-D945-8BD5-49A5C91D3FBB}" name="Table3" displayName="Table3" ref="A4:H11" totalsRowShown="0" headerRowDxfId="51" dataDxfId="52" headerRowBorderDxfId="61" tableBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E13F33F7-DB49-D945-8BD5-49A5C91D3FBB}" name="Table3" displayName="Table3" ref="A4:H11" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32">
   <autoFilter ref="A4:H11" xr:uid="{E13F33F7-DB49-D945-8BD5-49A5C91D3FBB}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C00EF0D9-1C7D-0D45-99D6-220E1DB117C9}" name=" " dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{1B8021CB-1B1B-5040-8E9D-2B801B2792AF}" name="k=1" dataDxfId="59"/>
-    <tableColumn id="3" xr3:uid="{8D754F41-93C4-8142-8028-7C43C11FE2CE}" name="k=3" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{0B864F61-33D7-9F40-8654-C46BD3C04C81}" name="k=5" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{70689DA2-967A-864F-BDCB-B14DFBC7D481}" name="k=7" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{67DA3227-2744-774B-9CD1-D02836B55989}" name="k=10" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{FA15949B-88B4-7F47-9863-B717F2B95F31}" name="k=13" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{0D1050DD-8B68-994E-9846-5FCFA3DCBB40}" name="k=15" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{C00EF0D9-1C7D-0D45-99D6-220E1DB117C9}" name=" " dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{1B8021CB-1B1B-5040-8E9D-2B801B2792AF}" name="k=1" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{8D754F41-93C4-8142-8028-7C43C11FE2CE}" name="k=3" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{0B864F61-33D7-9F40-8654-C46BD3C04C81}" name="k=5" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{70689DA2-967A-864F-BDCB-B14DFBC7D481}" name="k=7" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{67DA3227-2744-774B-9CD1-D02836B55989}" name="k=10" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{FA15949B-88B4-7F47-9863-B717F2B95F31}" name="k=13" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{0D1050DD-8B68-994E-9846-5FCFA3DCBB40}" name="k=15" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F95067DD-3104-2843-AAED-AFD1382B3766}" name="Table4" displayName="Table4" ref="A14:H21" totalsRowShown="0" headerRowDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F95067DD-3104-2843-AAED-AFD1382B3766}" name="Table4" displayName="Table4" ref="A14:H21" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="A14:H21" xr:uid="{F95067DD-3104-2843-AAED-AFD1382B3766}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{004E7071-6969-3244-A536-9FDD55082F9E}" name=" " dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{830D2BB0-05C6-6C4A-9F49-21894F56DB43}" name="k=1" dataDxfId="49">
+    <tableColumn id="1" xr3:uid="{004E7071-6969-3244-A536-9FDD55082F9E}" name=" " dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{830D2BB0-05C6-6C4A-9F49-21894F56DB43}" name="k=1" dataDxfId="21">
       <calculatedColumnFormula>B5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D155A4D5-53B0-8E43-8435-98EEE6E23CA0}" name="k=3" dataDxfId="48">
+    <tableColumn id="3" xr3:uid="{D155A4D5-53B0-8E43-8435-98EEE6E23CA0}" name="k=3" dataDxfId="20">
       <calculatedColumnFormula>C5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{47F4EC5B-5BEE-634D-9919-A3C24428D7FF}" name="k=5" dataDxfId="47">
+    <tableColumn id="4" xr3:uid="{47F4EC5B-5BEE-634D-9919-A3C24428D7FF}" name="k=5" dataDxfId="19">
       <calculatedColumnFormula>D5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6733A6A7-1EB2-AA4B-AE2C-0F66D59A16BC}" name="k=7" dataDxfId="46">
+    <tableColumn id="5" xr3:uid="{6733A6A7-1EB2-AA4B-AE2C-0F66D59A16BC}" name="k=7" dataDxfId="18">
       <calculatedColumnFormula>E5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{82413377-F9AB-374C-BEE4-87E67BFF2030}" name="k=10" dataDxfId="45">
+    <tableColumn id="6" xr3:uid="{82413377-F9AB-374C-BEE4-87E67BFF2030}" name="k=10" dataDxfId="17">
       <calculatedColumnFormula>F5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7F793414-9812-D545-AF8A-7BE8C6A5751E}" name="k=13" dataDxfId="44">
+    <tableColumn id="7" xr3:uid="{7F793414-9812-D545-AF8A-7BE8C6A5751E}" name="k=13" dataDxfId="16">
       <calculatedColumnFormula>G5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{26A99295-22E0-8546-939B-A3E9C7EB866E}" name="k=15" dataDxfId="43">
+    <tableColumn id="8" xr3:uid="{26A99295-22E0-8546-939B-A3E9C7EB866E}" name="k=15" dataDxfId="15">
       <calculatedColumnFormula>H5*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2014,17 +2007,17 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9412D6EA-F046-104F-871B-F988EF78132B}" name="Table1" displayName="Table1" ref="A11:D15" totalsRowShown="0" headerRowDxfId="70" dataDxfId="71" headerRowBorderDxfId="76" tableBorderDxfId="77">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9412D6EA-F046-104F-871B-F988EF78132B}" name="Table1" displayName="Table1" ref="A11:D15" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
   <autoFilter ref="A11:D15" xr:uid="{9412D6EA-F046-104F-871B-F988EF78132B}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3E423965-B55E-8040-A3BB-D9FE9E84D754}" name=" " dataDxfId="75"/>
-    <tableColumn id="2" xr3:uid="{0EEAA484-2E43-B442-BA20-4D83FA5E59C9}" name="Coarse (1 Mole)" dataDxfId="74">
+    <tableColumn id="1" xr3:uid="{3E423965-B55E-8040-A3BB-D9FE9E84D754}" name=" " dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{0EEAA484-2E43-B442-BA20-4D83FA5E59C9}" name="Coarse (1 Mole)" dataDxfId="9">
       <calculatedColumnFormula>B5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C9D42E43-2A4E-0744-9872-3507E686BED8}" name="Fine (1/2 Mole)" dataDxfId="73">
+    <tableColumn id="3" xr3:uid="{C9D42E43-2A4E-0744-9872-3507E686BED8}" name="Fine (1/2 Mole)" dataDxfId="8">
       <calculatedColumnFormula>C5*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FAE99FF8-0C2A-0447-93D3-71B7F5F3F784}" name="Fine (1/4 Mole)" dataDxfId="72">
+    <tableColumn id="4" xr3:uid="{FAE99FF8-0C2A-0447-93D3-71B7F5F3F784}" name="Fine (1/4 Mole)" dataDxfId="7">
       <calculatedColumnFormula>D5*1000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2033,13 +2026,13 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5BE913E8-B4BC-4A42-AB35-AA9E716BB54A}" name="Table2" displayName="Table2" ref="A4:D8" totalsRowShown="0" headerRowDxfId="63" headerRowBorderDxfId="68" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5BE913E8-B4BC-4A42-AB35-AA9E716BB54A}" name="Table2" displayName="Table2" ref="A4:D8" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4">
   <autoFilter ref="A4:D8" xr:uid="{5BE913E8-B4BC-4A42-AB35-AA9E716BB54A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3FBE9064-0F4C-7E4E-B7C5-060FCBCD407F}" name=" " dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{A6240EEA-8E2B-E345-BA53-B89462EFB8B7}" name="Coarse (1 Mole)" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{10D3B330-42BA-7041-BF91-AF053FF19FBB}" name="Fine (1/2 Mole)" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{5AD80CDD-B613-164C-9F0F-8C4E307462EC}" name="Fine (1/4 Mole)" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{3FBE9064-0F4C-7E4E-B7C5-060FCBCD407F}" name=" " dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{A6240EEA-8E2B-E345-BA53-B89462EFB8B7}" name="Coarse (1 Mole)" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{10D3B330-42BA-7041-BF91-AF053FF19FBB}" name="Fine (1/2 Mole)" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{5AD80CDD-B613-164C-9F0F-8C4E307462EC}" name="Fine (1/4 Mole)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2383,7 +2376,7 @@
     </row>
     <row r="4" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>0</v>
@@ -2585,7 +2578,7 @@
       <c r="G11" s="25">
         <v>7.0095062255859294E-5</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="7">
         <v>7.6055526733398397E-5</v>
       </c>
     </row>
@@ -2596,7 +2589,7 @@
     </row>
     <row r="14" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>0</v>
@@ -2883,7 +2876,7 @@
     </row>
     <row r="4" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>0</v>
@@ -3085,7 +3078,7 @@
       <c r="G11" s="25">
         <v>2.5987625122070299E-5</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="7">
         <v>3.5047531127929599E-5</v>
       </c>
     </row>
@@ -3106,7 +3099,7 @@
     </row>
     <row r="14" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>0</v>
@@ -3393,7 +3386,7 @@
     </row>
     <row r="4" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>0</v>
@@ -3595,7 +3588,7 @@
       <c r="G11" s="25">
         <v>1.21116638183593E-4</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="7">
         <v>1.5282630920410099E-4</v>
       </c>
     </row>
@@ -3609,7 +3602,7 @@
     </row>
     <row r="14" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>0</v>
@@ -3878,14 +3871,14 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" style="9" customWidth="1"/>
+    <col min="1" max="1" width="39.5" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="23" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -3895,7 +3888,7 @@
     </row>
     <row r="4" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>15</v>
@@ -3970,7 +3963,7 @@
     </row>
     <row r="11" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>15</v>
